--- a/data/INDA.xlsx
+++ b/data/INDA.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30.24414253234863</v>
+        <v>30.244140625</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29.62898254394531</v>
+        <v>29.62897682189941</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.57468605041504</v>
+        <v>30.57467842102051</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.13396644592285</v>
+        <v>30.13396453857422</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.22577667236328</v>
+        <v>30.22577857971191</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.22577667236328</v>
+        <v>30.22577857971191</v>
       </c>
     </row>
     <row r="8">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.27168655395508</v>
+        <v>30.27169036865234</v>
       </c>
     </row>
     <row r="9">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.06051635742188</v>
+        <v>30.06051445007324</v>
       </c>
     </row>
     <row r="10">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29.63815879821777</v>
+        <v>29.63815689086914</v>
       </c>
     </row>
     <row r="11">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.93196487426758</v>
+        <v>29.93196678161621</v>
       </c>
     </row>
     <row r="12">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30.2074146270752</v>
+        <v>30.20741844177246</v>
       </c>
     </row>
     <row r="13">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.30840873718262</v>
+        <v>30.30841636657715</v>
       </c>
     </row>
     <row r="14">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.0788745880127</v>
+        <v>30.07887268066406</v>
       </c>
     </row>
     <row r="15">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.85851860046387</v>
+        <v>29.8585147857666</v>
       </c>
     </row>
     <row r="16">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.16151428222656</v>
+        <v>30.16150665283203</v>
       </c>
     </row>
     <row r="18">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29.98705291748047</v>
+        <v>29.9870548248291</v>
       </c>
     </row>
     <row r="19">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29.44534301757812</v>
+        <v>29.44534492492676</v>
       </c>
     </row>
     <row r="20">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30.11559677124023</v>
+        <v>30.1156005859375</v>
       </c>
     </row>
     <row r="23">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29.82179069519043</v>
+        <v>29.8217887878418</v>
       </c>
     </row>
     <row r="24">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29.86769104003906</v>
+        <v>29.86769866943359</v>
       </c>
     </row>
     <row r="25">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>30.13396644592285</v>
+        <v>30.13396453857422</v>
       </c>
     </row>
     <row r="26">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>30.5012321472168</v>
+        <v>30.50123023986816</v>
       </c>
     </row>
     <row r="28">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>30.0696964263916</v>
+        <v>30.06969451904297</v>
       </c>
     </row>
     <row r="31">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29.55552673339844</v>
+        <v>29.5555248260498</v>
       </c>
     </row>
     <row r="32">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29.64733695983887</v>
+        <v>29.64734077453613</v>
       </c>
     </row>
     <row r="33">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.30761909484863</v>
+        <v>29.3076229095459</v>
       </c>
     </row>
     <row r="34">
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29.44534301757812</v>
+        <v>29.44534492492676</v>
       </c>
     </row>
     <row r="36">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.5188045501709</v>
+        <v>29.51880073547363</v>
       </c>
     </row>
     <row r="37">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>30.16151428222656</v>
+        <v>30.16150665283203</v>
       </c>
     </row>
     <row r="39">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>30.00542259216309</v>
+        <v>30.00542640686035</v>
       </c>
     </row>
     <row r="40">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29.75751876831055</v>
+        <v>29.75752067565918</v>
       </c>
     </row>
     <row r="41">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>30.01460266113281</v>
+        <v>30.01460456848145</v>
       </c>
     </row>
     <row r="42">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29.79425048828125</v>
+        <v>29.79424858093262</v>
       </c>
     </row>
     <row r="44">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>30.73995208740234</v>
+        <v>30.73995399475098</v>
       </c>
     </row>
     <row r="45">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>30.98785209655762</v>
+        <v>30.98785400390625</v>
       </c>
     </row>
     <row r="46">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>30.67568016052246</v>
+        <v>30.67567443847656</v>
       </c>
     </row>
     <row r="47">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>30.70321655273438</v>
+        <v>30.70322036743164</v>
       </c>
     </row>
     <row r="48">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>31.57547569274902</v>
+        <v>31.57546997070312</v>
       </c>
     </row>
     <row r="49">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>31.80501556396484</v>
+        <v>31.80501174926758</v>
       </c>
     </row>
     <row r="50">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>31.72237968444824</v>
+        <v>31.72237586975098</v>
       </c>
     </row>
     <row r="51">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31.85091781616211</v>
+        <v>31.85092353820801</v>
       </c>
     </row>
     <row r="52">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>32.20900726318359</v>
+        <v>32.20900344848633</v>
       </c>
     </row>
     <row r="53">
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>32.54872512817383</v>
+        <v>32.54872894287109</v>
       </c>
     </row>
     <row r="54">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.49363327026367</v>
+        <v>32.49362945556641</v>
       </c>
     </row>
     <row r="55">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32.74153137207031</v>
+        <v>32.74153900146484</v>
       </c>
     </row>
     <row r="56">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>32.63136291503906</v>
+        <v>32.63135147094727</v>
       </c>
     </row>
     <row r="57">
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.84173965454102</v>
+        <v>31.84173774719238</v>
       </c>
     </row>
     <row r="58">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.76828575134277</v>
+        <v>31.76828384399414</v>
       </c>
     </row>
     <row r="59">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>32.08045959472656</v>
+        <v>32.08046340942383</v>
       </c>
     </row>
     <row r="60">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31.78664970397949</v>
+        <v>31.78665351867676</v>
       </c>
     </row>
     <row r="61">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>32.36508941650391</v>
+        <v>32.36509323120117</v>
       </c>
     </row>
     <row r="63">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>32.69562530517578</v>
+        <v>32.69563293457031</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>32.8792610168457</v>
+        <v>32.87925720214844</v>
       </c>
     </row>
     <row r="65">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>32.98025512695312</v>
+        <v>32.98025894165039</v>
       </c>
     </row>
     <row r="66">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>32.61299514770508</v>
+        <v>32.61299133300781</v>
       </c>
     </row>
     <row r="67">
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>32.83335113525391</v>
+        <v>32.83334732055664</v>
       </c>
     </row>
     <row r="68">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>32.42018127441406</v>
+        <v>32.4201774597168</v>
       </c>
     </row>
     <row r="69">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>32.56708908081055</v>
+        <v>32.56707763671875</v>
       </c>
     </row>
     <row r="71">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>32.51199722290039</v>
+        <v>32.51200103759766</v>
       </c>
     </row>
     <row r="72">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>32.51199722290039</v>
+        <v>32.51200103759766</v>
       </c>
     </row>
     <row r="73">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>32.63136291503906</v>
+        <v>32.63135147094727</v>
       </c>
     </row>
     <row r="74">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>32.78744506835938</v>
+        <v>32.78744125366211</v>
       </c>
     </row>
     <row r="75">
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>32.9251708984375</v>
+        <v>32.92516326904297</v>
       </c>
     </row>
     <row r="76">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>32.86089324951172</v>
+        <v>32.86089706420898</v>
       </c>
     </row>
     <row r="77">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>32.15391540527344</v>
+        <v>32.15391159057617</v>
       </c>
     </row>
     <row r="78">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>32.22736740112305</v>
+        <v>32.22736358642578</v>
       </c>
     </row>
     <row r="80">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>32.61299514770508</v>
+        <v>32.61299133300781</v>
       </c>
     </row>
     <row r="82">
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>32.60380935668945</v>
+        <v>32.60380554199219</v>
       </c>
     </row>
     <row r="84">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>32.50281524658203</v>
+        <v>32.5028190612793</v>
       </c>
     </row>
     <row r="85">
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>32.35591125488281</v>
+        <v>32.35591506958008</v>
       </c>
     </row>
     <row r="86">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>32.66808700561523</v>
+        <v>32.66808319091797</v>
       </c>
     </row>
     <row r="87">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>31.41020393371582</v>
+        <v>31.41020011901855</v>
       </c>
     </row>
     <row r="89">
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>30.00542259216309</v>
+        <v>30.00542640686035</v>
       </c>
     </row>
     <row r="93">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>30.66649436950684</v>
+        <v>30.6664981842041</v>
       </c>
     </row>
     <row r="94">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30.48287200927734</v>
+        <v>30.48286247253418</v>
       </c>
     </row>
     <row r="95">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>30.85931777954102</v>
+        <v>30.85930824279785</v>
       </c>
     </row>
     <row r="96">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>30.96030807495117</v>
+        <v>30.96030426025391</v>
       </c>
     </row>
     <row r="97">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>32.13555145263672</v>
+        <v>32.13554763793945</v>
       </c>
     </row>
     <row r="100">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>32.53953552246094</v>
+        <v>32.5395393371582</v>
       </c>
     </row>
     <row r="102">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>32.70480728149414</v>
+        <v>32.70481109619141</v>
       </c>
     </row>
     <row r="103">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>32.47526931762695</v>
+        <v>32.47527313232422</v>
       </c>
     </row>
     <row r="104">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>32.78744506835938</v>
+        <v>32.78744125366211</v>
       </c>
     </row>
     <row r="105">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>33.03533935546875</v>
+        <v>33.03534317016602</v>
       </c>
     </row>
     <row r="106">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>33.40261077880859</v>
+        <v>33.40260314941406</v>
       </c>
     </row>
     <row r="107">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>33.31079483032227</v>
+        <v>33.310791015625</v>
       </c>
     </row>
     <row r="108">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>33.04453277587891</v>
+        <v>33.04452896118164</v>
       </c>
     </row>
     <row r="109">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>32.77826309204102</v>
+        <v>32.77825927734375</v>
       </c>
     </row>
     <row r="110">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>32.8792610168457</v>
+        <v>32.87925720214844</v>
       </c>
     </row>
     <row r="111">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>32.85171890258789</v>
+        <v>32.85171508789062</v>
       </c>
     </row>
     <row r="112">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>32.95270919799805</v>
+        <v>32.95271682739258</v>
       </c>
     </row>
     <row r="113">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>32.79662704467773</v>
+        <v>32.7966194152832</v>
       </c>
     </row>
     <row r="114">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>32.69562530517578</v>
+        <v>32.69563293457031</v>
       </c>
     </row>
     <row r="115">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>32.09454345703125</v>
+        <v>32.09453964233398</v>
       </c>
     </row>
     <row r="117">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>32.40955352783203</v>
+        <v>32.4095573425293</v>
       </c>
     </row>
     <row r="118">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>32.20571517944336</v>
+        <v>32.20572280883789</v>
       </c>
     </row>
     <row r="119">
@@ -1605,7 +1605,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>32.57632827758789</v>
+        <v>32.57633209228516</v>
       </c>
     </row>
     <row r="120">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>32.26131057739258</v>
+        <v>32.26131820678711</v>
       </c>
     </row>
     <row r="122">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>32.40955352783203</v>
+        <v>32.4095573425293</v>
       </c>
     </row>
     <row r="123">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>32.73383712768555</v>
+        <v>32.73384094238281</v>
       </c>
     </row>
     <row r="124">
@@ -1655,7 +1655,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>32.87281036376953</v>
+        <v>32.8728141784668</v>
       </c>
     </row>
     <row r="125">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>32.9839973449707</v>
+        <v>32.98400115966797</v>
       </c>
     </row>
     <row r="127">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>33.15077209472656</v>
+        <v>33.15076446533203</v>
       </c>
     </row>
     <row r="129">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>32.26131057739258</v>
+        <v>32.26131820678711</v>
       </c>
     </row>
     <row r="131">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>32.27984237670898</v>
+        <v>32.27983856201172</v>
       </c>
     </row>
     <row r="132">
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>32.15012359619141</v>
+        <v>32.1501350402832</v>
       </c>
     </row>
     <row r="134">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>32.32616424560547</v>
+        <v>32.32616806030273</v>
       </c>
     </row>
     <row r="136">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>32.48368072509766</v>
+        <v>32.48367691040039</v>
       </c>
     </row>
     <row r="137">
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>31.6590747833252</v>
+        <v>31.65907287597656</v>
       </c>
     </row>
     <row r="140">
@@ -1815,7 +1815,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>31.6776123046875</v>
+        <v>31.67760467529297</v>
       </c>
     </row>
     <row r="141">
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>31.15875816345215</v>
+        <v>31.15875625610352</v>
       </c>
     </row>
     <row r="144">
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>31.18655776977539</v>
+        <v>31.18655204772949</v>
       </c>
     </row>
     <row r="146">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>30.63991165161133</v>
+        <v>30.63990783691406</v>
       </c>
     </row>
     <row r="147">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>30.5750560760498</v>
+        <v>30.57505226135254</v>
       </c>
     </row>
     <row r="148">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>30.09326362609863</v>
+        <v>30.09325981140137</v>
       </c>
     </row>
     <row r="149">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>30.03766822814941</v>
+        <v>30.03767204284668</v>
       </c>
     </row>
     <row r="150">
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>29.57441329956055</v>
+        <v>29.57441520690918</v>
       </c>
     </row>
     <row r="152">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>29.38911247253418</v>
+        <v>29.38911056518555</v>
       </c>
     </row>
     <row r="153">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>29.98208045959473</v>
+        <v>29.98207855224609</v>
       </c>
     </row>
     <row r="155">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>29.80604362487793</v>
+        <v>29.80604553222656</v>
       </c>
     </row>
     <row r="156">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>29.67633056640625</v>
+        <v>29.67632865905762</v>
       </c>
     </row>
     <row r="157">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>29.34278297424316</v>
+        <v>29.34278678894043</v>
       </c>
     </row>
     <row r="159">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>29.81530570983887</v>
+        <v>29.8153076171875</v>
       </c>
     </row>
     <row r="160">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>29.59294700622559</v>
+        <v>29.59294891357422</v>
       </c>
     </row>
     <row r="161">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>29.40763854980469</v>
+        <v>29.40764045715332</v>
       </c>
     </row>
     <row r="163">
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>28.73128509521484</v>
+        <v>28.73128128051758</v>
       </c>
     </row>
     <row r="164">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>29.33351898193359</v>
+        <v>29.33352088928223</v>
       </c>
     </row>
     <row r="165">
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>29.79677581787109</v>
+        <v>29.79677772521973</v>
       </c>
     </row>
     <row r="166">
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>29.97280883789062</v>
+        <v>29.97281455993652</v>
       </c>
     </row>
     <row r="167">
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>29.67633056640625</v>
+        <v>29.67632865905762</v>
       </c>
     </row>
     <row r="168">
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>29.81530570983887</v>
+        <v>29.8153076171875</v>
       </c>
     </row>
     <row r="170">
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>29.06483268737793</v>
+        <v>29.0648307800293</v>
       </c>
     </row>
     <row r="171">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>29.25939750671387</v>
+        <v>29.2593994140625</v>
       </c>
     </row>
     <row r="172">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>29.75971603393555</v>
+        <v>29.75971794128418</v>
       </c>
     </row>
     <row r="175">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>29.70413017272949</v>
+        <v>29.70412445068359</v>
       </c>
     </row>
     <row r="176">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>30.01914405822754</v>
+        <v>30.01914215087891</v>
       </c>
     </row>
     <row r="177">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>29.98208045959473</v>
+        <v>29.98207855224609</v>
       </c>
     </row>
     <row r="178">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>30.31563377380371</v>
+        <v>30.31562995910645</v>
       </c>
     </row>
     <row r="179">
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>29.59294700622559</v>
+        <v>29.59294891357422</v>
       </c>
     </row>
     <row r="180">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>29.10189056396484</v>
+        <v>29.10189247131348</v>
       </c>
     </row>
     <row r="183">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>30.7603588104248</v>
+        <v>30.76035499572754</v>
       </c>
     </row>
     <row r="184">
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>31.13095855712891</v>
+        <v>31.13096237182617</v>
       </c>
     </row>
     <row r="186">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>31.00125503540039</v>
+        <v>31.00124740600586</v>
       </c>
     </row>
     <row r="189">
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>30.3712158203125</v>
+        <v>30.37121772766113</v>
       </c>
     </row>
     <row r="191">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>30.36194801330566</v>
+        <v>30.3619556427002</v>
       </c>
     </row>
     <row r="194">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>29.81530570983887</v>
+        <v>29.8153076171875</v>
       </c>
     </row>
     <row r="196">
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>30.35268592834473</v>
+        <v>30.35268783569336</v>
       </c>
     </row>
     <row r="198">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>30.51020050048828</v>
+        <v>30.51019477844238</v>
       </c>
     </row>
     <row r="199">
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>30.3804817199707</v>
+        <v>30.38048553466797</v>
       </c>
     </row>
     <row r="200">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>30.63991165161133</v>
+        <v>30.63990783691406</v>
       </c>
     </row>
     <row r="201">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>30.79741477966309</v>
+        <v>30.79742050170898</v>
       </c>
     </row>
     <row r="202">
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>31.18655776977539</v>
+        <v>31.18655204772949</v>
       </c>
     </row>
     <row r="203">
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>31.28846549987793</v>
+        <v>31.28847122192383</v>
       </c>
     </row>
     <row r="206">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>31.48303413391113</v>
+        <v>31.4830379486084</v>
       </c>
     </row>
     <row r="207">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>31.31626129150391</v>
+        <v>31.3162670135498</v>
       </c>
     </row>
     <row r="208">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>31.56642723083496</v>
+        <v>31.56642532348633</v>
       </c>
     </row>
     <row r="209">
@@ -2505,7 +2505,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>31.64054679870605</v>
+        <v>31.64054870605469</v>
       </c>
     </row>
     <row r="210">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>31.99262237548828</v>
+        <v>31.99262428283691</v>
       </c>
     </row>
     <row r="211">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>32.27984237670898</v>
+        <v>32.27983856201172</v>
       </c>
     </row>
     <row r="212">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>32.10380935668945</v>
+        <v>32.10380554199219</v>
       </c>
     </row>
     <row r="213">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>32.48368072509766</v>
+        <v>32.48367691040039</v>
       </c>
     </row>
     <row r="214">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>32.40955352783203</v>
+        <v>32.4095573425293</v>
       </c>
     </row>
     <row r="218">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>31.89070510864258</v>
+        <v>31.89070320129395</v>
       </c>
     </row>
     <row r="219">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>31.81658554077148</v>
+        <v>31.81658172607422</v>
       </c>
     </row>
     <row r="220">
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>31.61275291442871</v>
+        <v>31.61274909973145</v>
       </c>
     </row>
     <row r="221">
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>31.3811206817627</v>
+        <v>31.38112258911133</v>
       </c>
     </row>
     <row r="222">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>31.45524597167969</v>
+        <v>31.45524024963379</v>
       </c>
     </row>
     <row r="223">
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>31.6590747833252</v>
+        <v>31.65907287597656</v>
       </c>
     </row>
     <row r="224">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>31.71466445922852</v>
+        <v>31.71466827392578</v>
       </c>
     </row>
     <row r="226">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>31.91849708557129</v>
+        <v>31.91849899291992</v>
       </c>
     </row>
     <row r="227">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>31.76099014282227</v>
+        <v>31.76099586486816</v>
       </c>
     </row>
     <row r="228">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>31.6868724822998</v>
+        <v>31.68687057495117</v>
       </c>
     </row>
     <row r="229">
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>32.23351669311523</v>
+        <v>32.23351287841797</v>
       </c>
     </row>
     <row r="231">
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>32.48368072509766</v>
+        <v>32.48367691040039</v>
       </c>
     </row>
     <row r="232">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>31.92776298522949</v>
+        <v>31.92776870727539</v>
       </c>
     </row>
     <row r="233">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>31.84438323974609</v>
+        <v>31.84437370300293</v>
       </c>
     </row>
     <row r="235">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>32.25205612182617</v>
+        <v>32.25204849243164</v>
       </c>
     </row>
     <row r="236">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>32.2242546081543</v>
+        <v>32.22425079345703</v>
       </c>
     </row>
     <row r="237">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>31.89070510864258</v>
+        <v>31.89070320129395</v>
       </c>
     </row>
     <row r="238">
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>32.10380935668945</v>
+        <v>32.10380554199219</v>
       </c>
     </row>
     <row r="239">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>32.44661331176758</v>
+        <v>32.44661712646484</v>
       </c>
     </row>
     <row r="242">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>32.61338806152344</v>
+        <v>32.6133918762207</v>
       </c>
     </row>
     <row r="243">
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>32.40287017822266</v>
+        <v>32.40287399291992</v>
       </c>
     </row>
     <row r="244">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>32.69963455200195</v>
+        <v>32.69963073730469</v>
       </c>
     </row>
     <row r="245">
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>32.68108749389648</v>
+        <v>32.68109130859375</v>
       </c>
     </row>
     <row r="246">
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>32.8758430480957</v>
+        <v>32.87584686279297</v>
       </c>
     </row>
     <row r="248">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>32.7923698425293</v>
+        <v>32.79237365722656</v>
       </c>
     </row>
     <row r="249">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>32.59762954711914</v>
+        <v>32.59762573242188</v>
       </c>
     </row>
     <row r="254">
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>32.43997192382812</v>
+        <v>32.43996810913086</v>
       </c>
     </row>
     <row r="256">
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>32.01337051391602</v>
+        <v>32.01336669921875</v>
       </c>
     </row>
     <row r="258">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>32.43997192382812</v>
+        <v>32.43996810913086</v>
       </c>
     </row>
     <row r="259">
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>32.8758430480957</v>
+        <v>32.87584686279297</v>
       </c>
     </row>
     <row r="260">
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>33.02421951293945</v>
+        <v>33.02422714233398</v>
       </c>
     </row>
     <row r="261">
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>33.40444564819336</v>
+        <v>33.40444946289062</v>
       </c>
     </row>
     <row r="263">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>33.34880065917969</v>
+        <v>33.34880447387695</v>
       </c>
     </row>
     <row r="264">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>32.91294097900391</v>
+        <v>32.91293716430664</v>
       </c>
     </row>
     <row r="268">
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>33.00566864013672</v>
+        <v>33.00567245483398</v>
       </c>
     </row>
     <row r="270">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>32.59762954711914</v>
+        <v>32.59762573242188</v>
       </c>
     </row>
     <row r="271">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>32.7923698425293</v>
+        <v>32.79237365722656</v>
       </c>
     </row>
     <row r="273">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>32.33795547485352</v>
+        <v>32.33795166015625</v>
       </c>
     </row>
     <row r="277">
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>32.60689544677734</v>
+        <v>32.60689926147461</v>
       </c>
     </row>
     <row r="278">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>32.50488662719727</v>
+        <v>32.50487899780273</v>
       </c>
     </row>
     <row r="280">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>32.68108749389648</v>
+        <v>32.68109130859375</v>
       </c>
     </row>
     <row r="281">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>32.89439392089844</v>
+        <v>32.89438247680664</v>
       </c>
     </row>
     <row r="282">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>33.09841156005859</v>
+        <v>33.09841537475586</v>
       </c>
     </row>
     <row r="283">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>32.35650253295898</v>
+        <v>32.35650634765625</v>
       </c>
     </row>
     <row r="286">
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>32.72746658325195</v>
+        <v>32.72745513916016</v>
       </c>
     </row>
     <row r="287">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>32.29158401489258</v>
+        <v>32.29159164428711</v>
       </c>
     </row>
     <row r="289">
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>31.41056632995605</v>
+        <v>31.41056823730469</v>
       </c>
     </row>
     <row r="290">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>31.28073692321777</v>
+        <v>31.28073310852051</v>
       </c>
     </row>
     <row r="291">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>31.33638191223145</v>
+        <v>31.33638000488281</v>
       </c>
     </row>
     <row r="292">
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>30.78922653198242</v>
+        <v>30.78922080993652</v>
       </c>
     </row>
     <row r="293">
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>29.85256195068359</v>
+        <v>29.85256004333496</v>
       </c>
     </row>
     <row r="294">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>29.71345329284668</v>
+        <v>29.71345138549805</v>
       </c>
     </row>
     <row r="295">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>29.63925933837891</v>
+        <v>29.63926315307617</v>
       </c>
     </row>
     <row r="296">
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>26.89419746398926</v>
+        <v>26.89420127868652</v>
       </c>
     </row>
     <row r="300">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>27.77521514892578</v>
+        <v>27.77521705627441</v>
       </c>
     </row>
     <row r="301">
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>26.55106735229492</v>
+        <v>26.55106544494629</v>
       </c>
     </row>
     <row r="302">
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>26.25430297851562</v>
+        <v>26.25430107116699</v>
       </c>
     </row>
     <row r="304">
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="B307" t="n">
-        <v>21.1536808013916</v>
+        <v>21.15367698669434</v>
       </c>
     </row>
     <row r="308">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>21.39479827880859</v>
+        <v>21.39480018615723</v>
       </c>
     </row>
     <row r="309">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>20.05936431884766</v>
+        <v>20.05936241149902</v>
       </c>
     </row>
     <row r="311">
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="B311" t="n">
-        <v>21.58955001831055</v>
+        <v>21.58955192565918</v>
       </c>
     </row>
     <row r="312">
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>22.01614761352539</v>
+        <v>22.01614570617676</v>
       </c>
     </row>
     <row r="314">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>21.88631248474121</v>
+        <v>21.88631439208984</v>
       </c>
     </row>
     <row r="315">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>20.70853233337402</v>
+        <v>20.70853042602539</v>
       </c>
     </row>
     <row r="317">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>20.41176795959473</v>
+        <v>20.41177177429199</v>
       </c>
     </row>
     <row r="319">
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>21.95122909545898</v>
+        <v>21.95123291015625</v>
       </c>
     </row>
     <row r="320">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>22.59112739562988</v>
+        <v>22.59112930297852</v>
       </c>
     </row>
     <row r="321">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>23.35158348083496</v>
+        <v>23.35158538818359</v>
       </c>
     </row>
     <row r="322">
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>23.61125183105469</v>
+        <v>23.61124992370605</v>
       </c>
     </row>
     <row r="323">
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>23.39795112609863</v>
+        <v>23.39795303344727</v>
       </c>
     </row>
     <row r="324">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>22.94353294372559</v>
+        <v>22.94353485107422</v>
       </c>
     </row>
     <row r="326">
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>23.19392967224121</v>
+        <v>23.19392776489258</v>
       </c>
     </row>
     <row r="327">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>24.0471248626709</v>
+        <v>24.04712295532227</v>
       </c>
     </row>
     <row r="328">
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>23.62052345275879</v>
+        <v>23.62052536010742</v>
       </c>
     </row>
     <row r="329">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>22.87861824035645</v>
+        <v>22.87861442565918</v>
       </c>
     </row>
     <row r="330">
@@ -3715,7 +3715,7 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>24.07494163513184</v>
+        <v>24.07494354248047</v>
       </c>
     </row>
     <row r="331">
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>24.21405220031738</v>
+        <v>24.21405410766602</v>
       </c>
     </row>
     <row r="332">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>24.6870174407959</v>
+        <v>24.6870231628418</v>
       </c>
     </row>
     <row r="334">
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>24.62210273742676</v>
+        <v>24.62210464477539</v>
       </c>
     </row>
     <row r="335">
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>25.65149879455566</v>
+        <v>25.6515007019043</v>
       </c>
     </row>
     <row r="336">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>25.08579635620117</v>
+        <v>25.08579444885254</v>
       </c>
     </row>
     <row r="337">
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>24.66847229003906</v>
+        <v>24.66847038269043</v>
       </c>
     </row>
     <row r="339">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>24.18622970581055</v>
+        <v>24.18623352050781</v>
       </c>
     </row>
     <row r="340">
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>24.78903388977051</v>
+        <v>24.78902816772461</v>
       </c>
     </row>
     <row r="343">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>24.33461570739746</v>
+        <v>24.3346118927002</v>
       </c>
     </row>
     <row r="344">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>25.3918342590332</v>
+        <v>25.39183235168457</v>
       </c>
     </row>
     <row r="345">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>24.62210273742676</v>
+        <v>24.62210464477539</v>
       </c>
     </row>
     <row r="347">
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>24.1027660369873</v>
+        <v>24.10276794433594</v>
       </c>
     </row>
     <row r="348">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>24.39025688171387</v>
+        <v>24.3902530670166</v>
       </c>
     </row>
     <row r="349">
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>23.7039909362793</v>
+        <v>23.70398902893066</v>
       </c>
     </row>
     <row r="350">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>24.57573509216309</v>
+        <v>24.57573318481445</v>
       </c>
     </row>
     <row r="355">
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>25.49384689331055</v>
+        <v>25.49384307861328</v>
       </c>
     </row>
     <row r="357">
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>26.75509071350098</v>
+        <v>26.75508880615234</v>
       </c>
     </row>
     <row r="359">
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>27.10749816894531</v>
+        <v>27.10749626159668</v>
       </c>
     </row>
     <row r="362">
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>26.91275024414062</v>
+        <v>26.91274642944336</v>
       </c>
     </row>
     <row r="365">
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>24.82612800598145</v>
+        <v>24.82612609863281</v>
       </c>
     </row>
     <row r="366">
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>26.18938636779785</v>
+        <v>26.18938827514648</v>
       </c>
     </row>
     <row r="367">
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>25.77651405334473</v>
+        <v>25.77651214599609</v>
       </c>
     </row>
     <row r="369">
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>26.00898551940918</v>
+        <v>26.00898742675781</v>
       </c>
     </row>
     <row r="370">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>26.24145698547363</v>
+        <v>26.24145889282227</v>
       </c>
     </row>
     <row r="371">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>27.27363586425781</v>
+        <v>27.27363395690918</v>
       </c>
     </row>
     <row r="376">
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>26.98537063598633</v>
+        <v>26.98537254333496</v>
       </c>
     </row>
     <row r="379">
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>28.24072074890137</v>
+        <v>28.24072265625</v>
       </c>
     </row>
     <row r="381">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>28.83584976196289</v>
+        <v>28.83584785461426</v>
       </c>
     </row>
     <row r="382">
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>28.57547950744629</v>
+        <v>28.57548141479492</v>
       </c>
     </row>
     <row r="384">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>28.6126766204834</v>
+        <v>28.61267471313477</v>
       </c>
     </row>
     <row r="385">
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>28.8265495300293</v>
+        <v>28.82654762268066</v>
       </c>
     </row>
     <row r="390">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>29.3007926940918</v>
+        <v>29.30079078674316</v>
       </c>
     </row>
     <row r="391">
@@ -4325,7 +4325,7 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>29.7099437713623</v>
+        <v>29.70994758605957</v>
       </c>
     </row>
     <row r="392">
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>29.8773250579834</v>
+        <v>29.87732315063477</v>
       </c>
     </row>
     <row r="393">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>29.88662528991699</v>
+        <v>29.88662147521973</v>
       </c>
     </row>
     <row r="394">
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>29.95171165466309</v>
+        <v>29.95171737670898</v>
       </c>
     </row>
     <row r="396">
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>30.27717208862305</v>
+        <v>30.27717781066895</v>
       </c>
     </row>
     <row r="398">
@@ -4395,7 +4395,7 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>30.28647422790527</v>
+        <v>30.28647613525391</v>
       </c>
     </row>
     <row r="399">
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>29.95171165466309</v>
+        <v>29.95171737670898</v>
       </c>
     </row>
     <row r="400">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>29.70064353942871</v>
+        <v>29.70064735412598</v>
       </c>
     </row>
     <row r="401">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>30.10979461669922</v>
+        <v>30.10979270935059</v>
       </c>
     </row>
     <row r="403">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>30.24928092956543</v>
+        <v>30.2492790222168</v>
       </c>
     </row>
     <row r="404">
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="B404" t="n">
-        <v>30.53754043579102</v>
+        <v>30.53754425048828</v>
       </c>
     </row>
     <row r="405">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>30.42596054077148</v>
+        <v>30.42595863342285</v>
       </c>
     </row>
     <row r="406">
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>30.56544303894043</v>
+        <v>30.5654411315918</v>
       </c>
     </row>
     <row r="408">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>30.89090156555176</v>
+        <v>30.89090538024902</v>
       </c>
     </row>
     <row r="409">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>30.62123870849609</v>
+        <v>30.62123489379883</v>
       </c>
     </row>
     <row r="411">
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>30.86300277709961</v>
+        <v>30.86300468444824</v>
       </c>
     </row>
     <row r="412">
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>30.84440803527832</v>
+        <v>30.84440422058105</v>
       </c>
     </row>
     <row r="415">
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>31.24426078796387</v>
+        <v>31.2442569732666</v>
       </c>
     </row>
     <row r="417">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>31.5046272277832</v>
+        <v>31.50463104248047</v>
       </c>
     </row>
     <row r="419">
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>31.57902145385742</v>
+        <v>31.57901763916016</v>
       </c>
     </row>
     <row r="420">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>32.14624786376953</v>
+        <v>32.1462516784668</v>
       </c>
     </row>
     <row r="421">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>31.24426078796387</v>
+        <v>31.2442569732666</v>
       </c>
     </row>
     <row r="425">
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>31.0861759185791</v>
+        <v>31.08617973327637</v>
       </c>
     </row>
     <row r="426">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>30.67703056335449</v>
+        <v>30.67702865600586</v>
       </c>
     </row>
     <row r="427">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>31.24426078796387</v>
+        <v>31.2442569732666</v>
       </c>
     </row>
     <row r="428">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>31.35584831237793</v>
+        <v>31.3558464050293</v>
       </c>
     </row>
     <row r="429">
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>31.51392936706543</v>
+        <v>31.5139274597168</v>
       </c>
     </row>
     <row r="430">
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>31.87658500671387</v>
+        <v>31.8765869140625</v>
       </c>
     </row>
     <row r="431">
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>32.11835479736328</v>
+        <v>32.11836242675781</v>
       </c>
     </row>
     <row r="434">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>31.87658500671387</v>
+        <v>31.8765869140625</v>
       </c>
     </row>
     <row r="435">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>31.42093658447266</v>
+        <v>31.42094230651855</v>
       </c>
     </row>
     <row r="436">
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>31.09547805786133</v>
+        <v>31.09547424316406</v>
       </c>
     </row>
     <row r="437">
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>30.14699172973633</v>
+        <v>30.1469898223877</v>
       </c>
     </row>
     <row r="439">
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>31.21636581420898</v>
+        <v>31.21636199951172</v>
       </c>
     </row>
     <row r="441">
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>31.24426078796387</v>
+        <v>31.2442569732666</v>
       </c>
     </row>
     <row r="442">
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>31.48603248596191</v>
+        <v>31.48603057861328</v>
       </c>
     </row>
     <row r="443">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>31.95097541809082</v>
+        <v>31.95097351074219</v>
       </c>
     </row>
     <row r="444">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>31.69061279296875</v>
+        <v>31.69061088562012</v>
       </c>
     </row>
     <row r="445">
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>32.28573989868164</v>
+        <v>32.28573608398438</v>
       </c>
     </row>
     <row r="446">
@@ -4875,7 +4875,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>32.35083389282227</v>
+        <v>32.35082626342773</v>
       </c>
     </row>
     <row r="447">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>32.67628479003906</v>
+        <v>32.67629241943359</v>
       </c>
     </row>
     <row r="448">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>32.74137878417969</v>
+        <v>32.74138259887695</v>
       </c>
     </row>
     <row r="449">
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>33.0947380065918</v>
+        <v>33.09473419189453</v>
       </c>
     </row>
     <row r="450">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>32.93665313720703</v>
+        <v>32.93666076660156</v>
       </c>
     </row>
     <row r="451">
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>32.68559265136719</v>
+        <v>32.68558883666992</v>
       </c>
     </row>
     <row r="452">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>32.96455383300781</v>
+        <v>32.96455764770508</v>
       </c>
     </row>
     <row r="453">
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>32.38802719116211</v>
+        <v>32.38802337646484</v>
       </c>
     </row>
     <row r="455">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>32.58329772949219</v>
+        <v>32.58329391479492</v>
       </c>
     </row>
     <row r="457">
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>32.55540466308594</v>
+        <v>32.55540084838867</v>
       </c>
     </row>
     <row r="458">
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>31.87658500671387</v>
+        <v>31.8765869140625</v>
       </c>
     </row>
     <row r="461">
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>32.11835479736328</v>
+        <v>32.11836242675781</v>
       </c>
     </row>
     <row r="462">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>31.1884651184082</v>
+        <v>31.18846893310547</v>
       </c>
     </row>
     <row r="463">
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>31.23495674133301</v>
+        <v>31.23496246337891</v>
       </c>
     </row>
     <row r="465">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>31.32795143127441</v>
+        <v>31.32794952392578</v>
       </c>
     </row>
     <row r="466">
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>33.11333465576172</v>
+        <v>33.11334228515625</v>
       </c>
     </row>
     <row r="470">
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>33.89444351196289</v>
+        <v>33.89443969726562</v>
       </c>
     </row>
     <row r="471">
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>33.46669769287109</v>
+        <v>33.46669387817383</v>
       </c>
     </row>
     <row r="472">
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>33.67126846313477</v>
+        <v>33.67127227783203</v>
       </c>
     </row>
     <row r="473">
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>33.24352264404297</v>
+        <v>33.2435188293457</v>
       </c>
     </row>
     <row r="474">
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>34.16411590576172</v>
+        <v>34.16410827636719</v>
       </c>
     </row>
     <row r="476">
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>34.0432243347168</v>
+        <v>34.04322052001953</v>
       </c>
     </row>
     <row r="478">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>34.0432243347168</v>
+        <v>34.04322052001953</v>
       </c>
     </row>
     <row r="481">
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>34.25709533691406</v>
+        <v>34.25709915161133</v>
       </c>
     </row>
     <row r="483">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>34.38728332519531</v>
+        <v>34.38728713989258</v>
       </c>
     </row>
     <row r="484">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>34.9824104309082</v>
+        <v>34.98241424560547</v>
       </c>
     </row>
     <row r="486">
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>35.02890396118164</v>
+        <v>35.02890777587891</v>
       </c>
     </row>
     <row r="488">
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>35.36366271972656</v>
+        <v>35.36367034912109</v>
       </c>
     </row>
     <row r="489">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>35.6240348815918</v>
+        <v>35.62403869628906</v>
       </c>
     </row>
     <row r="490">
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>35.7170295715332</v>
+        <v>35.71702575683594</v>
       </c>
     </row>
     <row r="491">
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>35.68912887573242</v>
+        <v>35.68913269042969</v>
       </c>
     </row>
     <row r="492">
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>35.80255508422852</v>
+        <v>35.80255126953125</v>
       </c>
     </row>
     <row r="495">
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>36.34233474731445</v>
+        <v>36.34233856201172</v>
       </c>
     </row>
     <row r="496">
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>36.29580688476562</v>
+        <v>36.29580307006836</v>
       </c>
     </row>
     <row r="497">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>35.64434051513672</v>
+        <v>35.64434432983398</v>
       </c>
     </row>
     <row r="501">
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>36.25857925415039</v>
+        <v>36.25857543945312</v>
       </c>
     </row>
     <row r="502">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>37.10547256469727</v>
+        <v>37.1054801940918</v>
       </c>
     </row>
     <row r="505">
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>37.43120956420898</v>
+        <v>37.43121337890625</v>
       </c>
     </row>
     <row r="507">
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>38.07337188720703</v>
+        <v>38.07336807250977</v>
       </c>
     </row>
     <row r="510">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>37.89654159545898</v>
+        <v>37.89654541015625</v>
       </c>
     </row>
     <row r="511">
@@ -5545,7 +5545,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>38.92027282714844</v>
+        <v>38.92026901245117</v>
       </c>
     </row>
     <row r="514">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>38.14781951904297</v>
+        <v>38.14782333374023</v>
       </c>
     </row>
     <row r="517">
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>38.27811431884766</v>
+        <v>38.27811050415039</v>
       </c>
     </row>
     <row r="518">
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>39.07848358154297</v>
+        <v>39.07848739624023</v>
       </c>
     </row>
     <row r="519">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>38.48285293579102</v>
+        <v>38.48285675048828</v>
       </c>
     </row>
     <row r="521">
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>37.85000610351562</v>
+        <v>37.85001373291016</v>
       </c>
     </row>
     <row r="522">
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>37.84070205688477</v>
+        <v>37.8406982421875</v>
       </c>
     </row>
     <row r="523">
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>37.04964447021484</v>
+        <v>37.04964065551758</v>
       </c>
     </row>
     <row r="524">
@@ -5655,7 +5655,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>37.61733627319336</v>
+        <v>37.61734008789062</v>
       </c>
     </row>
     <row r="525">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>36.42610168457031</v>
+        <v>36.42609786987305</v>
       </c>
     </row>
     <row r="526">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>37.89654159545898</v>
+        <v>37.89654541015625</v>
       </c>
     </row>
     <row r="527">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>39.09709167480469</v>
+        <v>39.09709548950195</v>
       </c>
     </row>
     <row r="529">
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="B533" t="n">
-        <v>39.59034729003906</v>
+        <v>39.59035110473633</v>
       </c>
     </row>
     <row r="534">
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>40.02775955200195</v>
+        <v>40.02775573730469</v>
       </c>
     </row>
     <row r="536">
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>39.94400024414062</v>
+        <v>39.94399642944336</v>
       </c>
     </row>
     <row r="537">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>39.98122406005859</v>
+        <v>39.98122024536133</v>
       </c>
     </row>
     <row r="539">
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="B539" t="n">
-        <v>39.76717376708984</v>
+        <v>39.76716995239258</v>
       </c>
     </row>
     <row r="540">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>39.01333236694336</v>
+        <v>39.01333618164062</v>
       </c>
     </row>
     <row r="541">
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>39.42282485961914</v>
+        <v>39.42282867431641</v>
       </c>
     </row>
     <row r="542">
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>39.81370544433594</v>
+        <v>39.81370162963867</v>
       </c>
     </row>
     <row r="543">
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="B543" t="n">
-        <v>39.12501907348633</v>
+        <v>39.12501525878906</v>
       </c>
     </row>
     <row r="544">
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>38.1850471496582</v>
+        <v>38.18505096435547</v>
       </c>
     </row>
     <row r="545">
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>39.12501907348633</v>
+        <v>39.12501525878906</v>
       </c>
     </row>
     <row r="546">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>39.49728012084961</v>
+        <v>39.49727630615234</v>
       </c>
     </row>
     <row r="547">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>39.8230094909668</v>
+        <v>39.82301330566406</v>
       </c>
     </row>
     <row r="548">
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>39.43213272094727</v>
+        <v>39.43212890625</v>
       </c>
     </row>
     <row r="549">
@@ -5915,7 +5915,7 @@
         </is>
       </c>
       <c r="B550" t="n">
-        <v>39.32045745849609</v>
+        <v>39.32045364379883</v>
       </c>
     </row>
     <row r="551">
@@ -5955,7 +5955,7 @@
         </is>
       </c>
       <c r="B554" t="n">
-        <v>39.89746475219727</v>
+        <v>39.89746856689453</v>
       </c>
     </row>
     <row r="555">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="B555" t="n">
-        <v>39.76717376708984</v>
+        <v>39.76716995239258</v>
       </c>
     </row>
     <row r="556">
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>39.59034729003906</v>
+        <v>39.59035110473633</v>
       </c>
     </row>
     <row r="558">
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>39.51589584350586</v>
+        <v>39.51589202880859</v>
       </c>
     </row>
     <row r="560">
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>39.59965515136719</v>
+        <v>39.59965133666992</v>
       </c>
     </row>
     <row r="561">
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>38.93888473510742</v>
+        <v>38.93888854980469</v>
       </c>
     </row>
     <row r="563">
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>38.63175964355469</v>
+        <v>38.63176727294922</v>
       </c>
     </row>
     <row r="564">
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="B564" t="n">
-        <v>39.57173538208008</v>
+        <v>39.57172775268555</v>
       </c>
     </row>
     <row r="565">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>39.44144058227539</v>
+        <v>39.44144439697266</v>
       </c>
     </row>
     <row r="569">
@@ -6155,7 +6155,7 @@
         </is>
       </c>
       <c r="B574" t="n">
-        <v>37.37537002563477</v>
+        <v>37.37537384033203</v>
       </c>
     </row>
     <row r="575">
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>37.63595581054688</v>
+        <v>37.63595962524414</v>
       </c>
     </row>
     <row r="576">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>38.07337188720703</v>
+        <v>38.07336807250977</v>
       </c>
     </row>
     <row r="577">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>38.25018692016602</v>
+        <v>38.25019073486328</v>
       </c>
     </row>
     <row r="578">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>38.33395385742188</v>
+        <v>38.33395004272461</v>
       </c>
     </row>
     <row r="579">
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="B580" t="n">
-        <v>36.7890510559082</v>
+        <v>36.78905868530273</v>
       </c>
     </row>
     <row r="581">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>37.04033660888672</v>
+        <v>37.04033279418945</v>
       </c>
     </row>
     <row r="583">
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>37.27300262451172</v>
+        <v>37.27299880981445</v>
       </c>
     </row>
     <row r="584">
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>37.82209014892578</v>
+        <v>37.82208633422852</v>
       </c>
     </row>
     <row r="585">
@@ -6275,7 +6275,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>38.6876106262207</v>
+        <v>38.68760299682617</v>
       </c>
     </row>
     <row r="587">
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>38.17574310302734</v>
+        <v>38.17573928833008</v>
       </c>
     </row>
     <row r="589">
@@ -6305,7 +6305,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>38.64106750488281</v>
+        <v>38.64107513427734</v>
       </c>
     </row>
     <row r="590">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>39.27391815185547</v>
+        <v>39.27392196655273</v>
       </c>
     </row>
     <row r="593">
@@ -6345,7 +6345,7 @@
         </is>
       </c>
       <c r="B593" t="n">
-        <v>39.7764778137207</v>
+        <v>39.77648162841797</v>
       </c>
     </row>
     <row r="594">
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="B596" t="n">
-        <v>38.44562911987305</v>
+        <v>38.44563293457031</v>
       </c>
     </row>
     <row r="597">
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>39.0040283203125</v>
+        <v>39.00403213500977</v>
       </c>
     </row>
     <row r="598">
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>39.49728012084961</v>
+        <v>39.49727630615234</v>
       </c>
     </row>
     <row r="599">
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>39.89746475219727</v>
+        <v>39.89746856689453</v>
       </c>
     </row>
     <row r="600">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>40.15805435180664</v>
+        <v>40.15805053710938</v>
       </c>
     </row>
     <row r="601">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>40.20458221435547</v>
+        <v>40.20458602905273</v>
       </c>
     </row>
     <row r="602">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>40.20458221435547</v>
+        <v>40.20458602905273</v>
       </c>
     </row>
     <row r="603">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>41.01425933837891</v>
+        <v>41.01425552368164</v>
       </c>
     </row>
     <row r="607">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>41.20970153808594</v>
+        <v>41.20969390869141</v>
       </c>
     </row>
     <row r="609">
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>41.85185623168945</v>
+        <v>41.85186004638672</v>
       </c>
     </row>
     <row r="612">
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>42.23342895507812</v>
+        <v>42.23342514038086</v>
       </c>
     </row>
     <row r="613">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>42.24273300170898</v>
+        <v>42.24272918701172</v>
       </c>
     </row>
     <row r="614">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>42.20755386352539</v>
+        <v>42.20755004882812</v>
       </c>
     </row>
     <row r="617">
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>42.10507965087891</v>
+        <v>42.10508346557617</v>
       </c>
     </row>
     <row r="619">
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="B619" t="n">
-        <v>41.92808532714844</v>
+        <v>41.92809295654297</v>
       </c>
     </row>
     <row r="620">
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>40.9686164855957</v>
+        <v>40.96862030029297</v>
       </c>
     </row>
     <row r="623">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>41.52753829956055</v>
+        <v>41.52753448486328</v>
       </c>
     </row>
     <row r="624">
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="B631" t="n">
-        <v>41.0897216796875</v>
+        <v>41.08971405029297</v>
       </c>
     </row>
     <row r="632">
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>41.35054779052734</v>
+        <v>41.35054397583008</v>
       </c>
     </row>
     <row r="633">
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="B635" t="n">
-        <v>40.89409637451172</v>
+        <v>40.89410018920898</v>
       </c>
     </row>
     <row r="636">
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>41.31328582763672</v>
+        <v>41.31327819824219</v>
       </c>
     </row>
     <row r="638">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>41.15492248535156</v>
+        <v>41.15492630004883</v>
       </c>
     </row>
     <row r="639">
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>41.40643310546875</v>
+        <v>41.40644073486328</v>
       </c>
     </row>
     <row r="640">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>40.81026077270508</v>
+        <v>40.81025695800781</v>
       </c>
     </row>
     <row r="643">
@@ -6855,7 +6855,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>41.15492248535156</v>
+        <v>41.15492630004883</v>
       </c>
     </row>
     <row r="645">
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="B645" t="n">
-        <v>41.39711761474609</v>
+        <v>41.39712142944336</v>
       </c>
     </row>
     <row r="646">
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="B646" t="n">
-        <v>41.47164154052734</v>
+        <v>41.47164535522461</v>
       </c>
     </row>
     <row r="647">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>41.74178695678711</v>
+        <v>41.74179077148438</v>
       </c>
     </row>
     <row r="648">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>41.37848663330078</v>
+        <v>41.37849044799805</v>
       </c>
     </row>
     <row r="650">
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>41.63000106811523</v>
+        <v>41.6300048828125</v>
       </c>
     </row>
     <row r="652">
@@ -6935,7 +6935,7 @@
         </is>
       </c>
       <c r="B652" t="n">
-        <v>41.69520568847656</v>
+        <v>41.69520950317383</v>
       </c>
     </row>
     <row r="653">
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="B654" t="n">
-        <v>42.5335807800293</v>
+        <v>42.53358459472656</v>
       </c>
     </row>
     <row r="655">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>42.54290008544922</v>
+        <v>42.54289627075195</v>
       </c>
     </row>
     <row r="657">
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>42.71057510375977</v>
+        <v>42.7105712890625</v>
       </c>
     </row>
     <row r="661">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>43.05524063110352</v>
+        <v>43.05524444580078</v>
       </c>
     </row>
     <row r="662">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>43.29743576049805</v>
+        <v>43.29743957519531</v>
       </c>
     </row>
     <row r="663">
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>43.1856575012207</v>
+        <v>43.18565368652344</v>
       </c>
     </row>
     <row r="664">
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>43.1856575012207</v>
+        <v>43.18565368652344</v>
       </c>
     </row>
     <row r="668">
@@ -7125,7 +7125,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>44.31280136108398</v>
+        <v>44.31280517578125</v>
       </c>
     </row>
     <row r="672">
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>44.72267913818359</v>
+        <v>44.72267532348633</v>
       </c>
     </row>
     <row r="673">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>45.27227401733398</v>
+        <v>45.27227783203125</v>
       </c>
     </row>
     <row r="674">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>45.82187652587891</v>
+        <v>45.82188034057617</v>
       </c>
     </row>
     <row r="676">
@@ -7185,7 +7185,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>46.00818634033203</v>
+        <v>46.00818252563477</v>
       </c>
     </row>
     <row r="678">
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>46.46463775634766</v>
+        <v>46.46463394165039</v>
       </c>
     </row>
     <row r="684">
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>46.52052688598633</v>
+        <v>46.52052307128906</v>
       </c>
     </row>
     <row r="685">
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>45.53310394287109</v>
+        <v>45.53310775756836</v>
       </c>
     </row>
     <row r="687">
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>46.64162445068359</v>
+        <v>46.64162826538086</v>
       </c>
     </row>
     <row r="690">
@@ -7355,7 +7355,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>45.35611343383789</v>
+        <v>45.35611724853516</v>
       </c>
     </row>
     <row r="695">
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>46.5484733581543</v>
+        <v>46.54846954345703</v>
       </c>
     </row>
     <row r="704">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>47.04218292236328</v>
+        <v>47.04217910766602</v>
       </c>
     </row>
     <row r="706">
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>47.07012557983398</v>
+        <v>47.07012176513672</v>
       </c>
     </row>
     <row r="707">
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>46.73477554321289</v>
+        <v>46.73477172851562</v>
       </c>
     </row>
     <row r="709">
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>46.00818634033203</v>
+        <v>46.00818252563477</v>
       </c>
     </row>
     <row r="711">
@@ -7535,7 +7535,7 @@
         </is>
       </c>
       <c r="B712" t="n">
-        <v>46.46463775634766</v>
+        <v>46.46463394165039</v>
       </c>
     </row>
     <row r="713">
@@ -7575,7 +7575,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>46.05475616455078</v>
+        <v>46.05475997924805</v>
       </c>
     </row>
     <row r="717">
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="B718" t="n">
-        <v>46.24106979370117</v>
+        <v>46.24106597900391</v>
       </c>
     </row>
     <row r="719">
@@ -7605,7 +7605,7 @@
         </is>
       </c>
       <c r="B719" t="n">
-        <v>46.23175048828125</v>
+        <v>46.23175430297852</v>
       </c>
     </row>
     <row r="720">
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>46.56710433959961</v>
+        <v>46.56710052490234</v>
       </c>
     </row>
     <row r="721">
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>47.21917343139648</v>
+        <v>47.21916961669922</v>
       </c>
     </row>
     <row r="722">
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="B722" t="n">
-        <v>46.79998779296875</v>
+        <v>46.79998397827148</v>
       </c>
     </row>
     <row r="723">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="B723" t="n">
-        <v>46.576416015625</v>
+        <v>46.57641983032227</v>
       </c>
     </row>
     <row r="724">
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>46.73477554321289</v>
+        <v>46.73477172851562</v>
       </c>
     </row>
     <row r="725">
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>47.30301284790039</v>
+        <v>47.30300521850586</v>
       </c>
     </row>
     <row r="726">
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>46.37148284912109</v>
+        <v>46.37147903442383</v>
       </c>
     </row>
     <row r="730">
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>45.2909049987793</v>
+        <v>45.29090881347656</v>
       </c>
     </row>
     <row r="732">
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>45.2909049987793</v>
+        <v>45.29090881347656</v>
       </c>
     </row>
     <row r="734">
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>43.94019317626953</v>
+        <v>43.94018936157227</v>
       </c>
     </row>
     <row r="735">
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>44.46185302734375</v>
+        <v>44.46184921264648</v>
       </c>
     </row>
     <row r="740">
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="B742" t="n">
-        <v>45.13254928588867</v>
+        <v>45.13255310058594</v>
       </c>
     </row>
     <row r="743">
@@ -7895,7 +7895,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>44.16686630249023</v>
+        <v>44.16686248779297</v>
       </c>
     </row>
     <row r="749">
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>43.6915283203125</v>
+        <v>43.69152450561523</v>
       </c>
     </row>
     <row r="752">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>44.32530975341797</v>
+        <v>44.32531356811523</v>
       </c>
     </row>
     <row r="753">
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>44.66201019287109</v>
+        <v>44.66200637817383</v>
       </c>
     </row>
     <row r="754">
